--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -1498,11 +1498,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>St.Hammar, Gtl</t>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 49884-2023 artfynd.xlsx
+++ b/artfynd/A 49884-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222504</v>
       </c>
       <c r="B2" t="n">
-        <v>91961</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137222508</v>
       </c>
       <c r="B3" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137222502</v>
       </c>
       <c r="B4" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137221648</v>
       </c>
       <c r="B5" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137222501</v>
       </c>
       <c r="B6" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137222987</v>
       </c>
       <c r="B7" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>137222506</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>137222505</v>
       </c>
       <c r="B9" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137222507</v>
       </c>
       <c r="B10" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
